--- a/04-northbridge-cloudworks-grc-program/03-third-party-risk-management/artifacts/Northbridge-Third-Party-Risk-Assessment.xlsx
+++ b/04-northbridge-cloudworks-grc-program/03-third-party-risk-management/artifacts/Northbridge-Third-Party-Risk-Assessment.xlsx
@@ -2073,7 +2073,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="45" customHeight="1">
       <c r="A17" s="31" t="inlineStr">
         <is>
           <t>Incident Response</t>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>No tabletop evidence</t>
+          <t>Unable to test — evidence not provided. No tabletop evidence (F-004).</t>
         </is>
       </c>
       <c r="E17" s="31" t="n">
@@ -2918,7 +2918,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="65" customHeight="1">
       <c r="A5" s="31" t="inlineStr">
         <is>
           <t>F-004</t>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="E5" s="31" t="inlineStr">
         <is>
-          <t>Vendor provided incident-response plan but no recent exercise report.</t>
+          <t>Unable to test — evidence not provided. Vendor provided incident-response plan but no recent exercise report.</t>
         </is>
       </c>
       <c r="F5" s="31" t="inlineStr">

--- a/04-northbridge-cloudworks-grc-program/03-third-party-risk-management/artifacts/Northbridge-Third-Party-Risk-Assessment.xlsx
+++ b/04-northbridge-cloudworks-grc-program/03-third-party-risk-management/artifacts/Northbridge-Third-Party-Risk-Assessment.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Findings Register'!$A$1:$K$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Remediation Tracker'!$A$1:$H$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Decision Memo'!$A$1:$D$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'References'!$A$1:$C$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'References'!$A$1:$C$13</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="B9" s="55" t="n">
-        <v>46247</v>
+        <v>46260</v>
       </c>
       <c r="D9" s="31">
         <f>'Scorecard'!A7</f>
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="D8" s="60" t="n">
-        <v>46612</v>
+        <v>46625</v>
       </c>
     </row>
     <row r="9">
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="D12" s="55" t="n">
-        <v>46247</v>
+        <v>46260</v>
       </c>
     </row>
   </sheetData>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="F2" s="61">
-        <f>DATEDIF(DATE(2026,8,13),D2,"d")</f>
+        <f>D2-'Vendor Profile'!$D$12</f>
         <v/>
       </c>
       <c r="G2" s="30" t="inlineStr">
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="F3" s="62">
-        <f>DATEDIF(DATE(2026,8,13),D3,"d")</f>
+        <f>D3-'Vendor Profile'!$D$12</f>
         <v/>
       </c>
       <c r="G3" s="31" t="inlineStr">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="F4" s="62">
-        <f>DATEDIF(DATE(2026,8,13),D4,"d")</f>
+        <f>D4-'Vendor Profile'!$D$12</f>
         <v/>
       </c>
       <c r="G4" s="31" t="inlineStr">
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="F5" s="62">
-        <f>DATEDIF(DATE(2026,8,13),D5,"d")</f>
+        <f>D5-'Vendor Profile'!$D$12</f>
         <v/>
       </c>
       <c r="G5" s="31" t="inlineStr">
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="F6" s="63">
-        <f>DATEDIF(DATE(2026,8,13),D6,"d")</f>
+        <f>D6-'Vendor Profile'!$D$12</f>
         <v/>
       </c>
       <c r="G6" s="32" t="inlineStr">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="D8" s="60" t="n">
-        <v>46612</v>
+        <v>46625</v>
       </c>
     </row>
     <row r="9">
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="D9" s="60" t="n">
-        <v>46247</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="10">
@@ -3514,7 +3514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3726,6 +3726,23 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>Scenario dates and rating definitions</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>Fictional assessment assumptions; see shared company profile</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>../../00-company-profile/Northbridge-Company-and-GRC-Scope.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
